--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupPrintArea/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupPrintArea/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5026fe76decf4792"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3e642ad4569a4c39"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$1,'Sheet1'!$A$3:$A$3</x:definedName>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupPrintArea/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupPrintArea/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3e642ad4569a4c39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rca953e043aa04cde"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$1,'Sheet1'!$A$3:$A$3</x:definedName>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupPrintArea/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupPrintArea/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rca953e043aa04cde"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R26a63e72791f4596"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$1,'Sheet1'!$A$3:$A$3</x:definedName>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupPrintArea/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupPrintArea/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R26a63e72791f4596"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rba34a75dc710481f"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$1,'Sheet1'!$A$3:$A$3</x:definedName>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupPrintArea/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupPrintArea/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rba34a75dc710481f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9f2bb3d05e0840c5"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$1,'Sheet1'!$A$3:$A$3</x:definedName>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupPrintArea/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupPrintArea/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9f2bb3d05e0840c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra5e6a4a13a7a4aa8"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$1,'Sheet1'!$A$3:$A$3</x:definedName>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupPrintArea/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupPrintArea/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra5e6a4a13a7a4aa8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdaec318e802f4836"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$1,'Sheet1'!$A$3:$A$3</x:definedName>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupPrintArea/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupPrintArea/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdaec318e802f4836"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7feadfef244a48ea"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$1,'Sheet1'!$A$3:$A$3</x:definedName>
